--- a/02_加值成品/八上/八上2-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上2-1_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上2-1 認識物質的性質　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二上學期 八上2-1 認識物質的性質　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>顏色、密度屬於哪種性質？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>固液氣</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>不一定</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>物理性質</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>有新物質生成</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>種類不變</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>可燃性屬於哪種性質？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>化學性質</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>皆固定</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>物理性質</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>不一定</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>生成新物質</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>固態物質的形狀與體積？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>有新物質生成</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>化學性質</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>皆固定</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>固液氣</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>固態特徵</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>氣態物質的形狀與體積？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>皆可變</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>化學性質</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>不一定</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>物理變化</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>氣態特徵</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>融冰屬於哪種變化？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>物理變化</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>皆可變</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>固液氣</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>化學性質</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>仍是水</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>燃燒屬於哪種變化？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>化學變化</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>有新物質生成</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>不一定</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>化學性質</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>生成新物質</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>沸點熔點屬於哪種性質？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>固液氣</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>物理變化</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>物理性質</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>皆固定</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>可測量</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>生鏽屬於哪種變化？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>化學變化</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>皆可變</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>固液氣</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>化學性質</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>生成氧化鐵</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>物質的三態是哪三態？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>皆固定</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>物理性質</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>化學變化</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>固液氣</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>三態</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>水結冰屬哪種變化？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>皆可變</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>物理變化</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>不一定</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>仍是水</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上2-1 認識物質的性質　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二上學期 八上2-1 認識物質的性質　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>化學變化常見哪些徵象？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>光/熱/氣體/沉澱/變色</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>乾冰昇華、冰熔化皆物理變化</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>物理性質(如密度沸點)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>鐵與氧生成氧化鐵</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>伴隨現象</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>切紙屬何變化？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>物理性質</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>化學變化</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>物理變化</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>皆可變</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>仍是紙</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>液態的形狀與體積？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>鐵與氧水生成新物質氧化鐵</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>乾冰昇華、冰熔化皆物理變化</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>體積固定形狀可變</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>種類不變只是狀態改變</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>液態特徵</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>鎂帶燃燒是何變化？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>物理性質</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>皆可變</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>化學變化</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>有新物質生成</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>生成氧化鎂</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>溶解度屬何性質？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>物理性質</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>物理變化</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>皆固定</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>固液氣</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>可觀測</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>食物腐敗是何變化？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>有新物質生成</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>化學性質</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>皆固定</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>化學變化</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>產生新物質</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>水沸騰成水蒸氣是何變化？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>物理變化</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>皆可變</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>化學性質</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>皆固定</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>仍是水</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>與酸反應能力屬何性質？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>化學變化</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>有新物質生成</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>物理性質</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>化學性質</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>化學反應</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>物理變化中物質種類會改變嗎？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>皆固定</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>物理性質</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>化學性質</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>不會</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>無新物質</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>紙張燃燒生成灰燼屬何變化？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>物理變化</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>化學變化</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>有新物質生成</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>皆可變</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>新物質</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上2-1 認識物質的性質　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二上學期 八上2-1 認識物質的性質　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>顏色變化就一定是化學變化嗎？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>不一定</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>化學性質</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>皆可變</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>有新物質生成</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>須看是否生成新物質</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>如何判斷發生化學變化？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>物理性質</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>皆固定</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>有新物質生成</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>皆可變</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>觀察徵象</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>三態變化為何是物理變化？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>鐵與氧水生成新物質氧化鐵</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>種類不變只是狀態改變</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>光/熱/氣體/沉澱/變色</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>體積固定形狀可變</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>無新物質</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>點蠟燭同時有幾種變化？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>種類不變只是狀態改變</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>光/熱/氣體/沉澱/變色</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>物理性質(如密度沸點)</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>物理(熔)與化學(燃)</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>複合變化</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>鐵磨成粉末是何變化？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>皆固定</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>固液氣</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>化學變化</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>物理變化</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>仍是鐵</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>為何生鏽是化學變化？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>物理性質(如密度沸點)</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>體積固定形狀可變</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>鐵與氧生成氧化鐵</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>鐵與氧水生成新物質氧化鐵</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>新物質</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>乾冰昇華是何變化？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>不一定</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>有新物質生成</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>物理變化</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>化學性質</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>固→氣仍是CO₂</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>判別物質種類可用哪類性質？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>鐵與氧水生成新物質氧化鐵</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>物理(熔)與化學(燃)</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>種類不變只是狀態改變</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>物理性質(如密度沸點)</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>特性辨別</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>乾冰與冰的變化過程差別？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>鐵與氧水生成新物質氧化鐵</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>物理(熔)與化學(燃)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>光/熱/氣體/沉澱/變色</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>乾冰昇華、冰熔化皆物理變化</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>物態</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>鐵在潮濕空氣生鏽為何是化學變化？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>光/熱/氣體/沉澱/變色</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>體積固定形狀可變</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>鐵與氧水生成新物質氧化鐵</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>物理(熔)與化學(燃)</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>氧化</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八上/八上2-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上2-1_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>種類不變</t>
+          <t>種類不變：觀察顏色、密度等性質時，物質的種類本身不會改變，所以屬於物理性質</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>生成新物質</t>
+          <t>生成新物質：物質燃燒後會產生和原本完全不同的新物質，所以可燃性是化學性質</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>固態特徵</t>
+          <t>固態特徵：固態物質的分子排列緊密固定，所以形狀和體積都不容易改變</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>氣態特徵</t>
+          <t>氣態特徵：氣態物質的分子間距離大、能自由運動，所以形狀和體積都會隨容器改變</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>仍是水</t>
+          <t>仍是水：冰融化只是從固態變成液態，化學成分仍然是水，沒有生成新物質，屬於物理變化</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>生成新物質</t>
+          <t>生成新物質：物質燃燒後會產生灰燼、氣體等和原本性質完全不同的新物質，屬於化學變化</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>可測量</t>
+          <t>可測量：沸點、熔點是可以直接觀察測量、不需要產生新物質就能得知的性質，屬於物理性質</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>生成氧化鐵</t>
+          <t>生成氧化鐵：鐵生鏽是和氧氣、水分反應生成氧化鐵這種新物質的過程，屬於化學變化</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>三態</t>
+          <t>三態：物質常見的三種狀態是固態、液態、氣態，合稱三態</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>仍是水</t>
+          <t>仍是水：水結冰只是狀態從液態變成固態，化學成分仍然是水，沒有變成新物質，屬於物理變化</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>伴隨現象</t>
+          <t>伴隨現象：化學變化發生時常常伴隨發光、放熱、產生氣體、生成沉澱或顏色改變等現象，可以幫助判斷是否發生了化學變化</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>仍是紙</t>
+          <t>仍是紙：紙被剪切後只是形狀改變，化學成分仍然是紙，沒有生成新物質，屬於物理變化</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>液態特徵</t>
+          <t>液態特徵：液態物質的體積固定，但會隨容器改變形狀，這是液態的特徵</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>生成氧化鎂</t>
+          <t>生成氧化鎂：鎂帶燃燒後和氧結合生成氧化鎂這種新物質，屬於化學變化</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>可觀測</t>
+          <t>可觀測：溶解度是指某物質在特定溶劑中能溶解的量，可以直接觀測測量，不涉及新物質生成，屬於物理性質</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>產生新物質</t>
+          <t>產生新物質：食物腐敗過程中微生物分解食物成分，產生和原本不同的新物質(如酸敗氣味的化合物)，屬於化學變化</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>仍是水</t>
+          <t>仍是水：水沸騰只是從液態變成氣態，化學成分仍然是水，沒有生成新物質，屬於物理變化</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>化學反應</t>
+          <t>化學反應：一種物質能否與酸反應，需要透過實際發生化學反應才能觀察出來，屬於化學性質</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>無新物質</t>
+          <t>無新物質：物理變化只改變物質的形狀、狀態等外觀，不會產生新物質，物質種類不變</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>新物質</t>
+          <t>新物質：紙張燃燒後產生灰燼、二氧化碳等和原本紙張性質完全不同的新物質，屬於化學變化</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>須看是否生成新物質</t>
+          <t>須看是否生成新物質：判斷是否為化學變化的關鍵在於有沒有生成新物質，有些顏色改變(如混合顏料)並沒有生成新物質，只是物理變化</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>觀察徵象</t>
+          <t>觀察徵象：判斷是否發生化學變化的核心標準是有沒有生成性質不同的新物質，可透過觀察發光、放熱、產生氣體或沉澱等徵象輔助判斷</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>無新物質</t>
+          <t>無新物質：物質在固、液、氣三態之間轉變時，分子本身的化學組成沒有改變，只是排列方式和運動狀態不同，沒有生成新物質，所以是物理變化</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>複合變化</t>
+          <t>複合變化：蠟燭燃燒時，蠟先受熱熔化成液態(物理變化)，接著蠟油與氧燃燒生成二氧化碳和水(化學變化)，同時包含兩種變化</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>仍是鐵</t>
+          <t>仍是鐵：鐵塊磨成粉末只是形狀和顆粒大小改變，化學成分仍然是鐵，沒有生成新物質，屬於物理變化</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>新物質</t>
+          <t>新物質：生鏽是鐵和空氣中的氧、水分反應，生成性質和鐵完全不同的氧化鐵，因為產生了新物質，所以是化學變化</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>固→氣仍是CO₂</t>
+          <t>固→氣仍是CO₂：乾冰(固態二氧化碳)受熱直接變成氣態的二氧化碳，化學成分沒有改變，只是狀態從固態變成氣態，屬於物理變化</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>特性辨別</t>
+          <t>特性辨別：密度、沸點等物理性質是每種物質固有的特徵值，不需要破壞或改變物質就能測量，可以用來幫助辨別是哪一種物質</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>物態</t>
+          <t>物態：乾冰(固態二氧化碳)受熱會直接變成氣體，這種固態直接變氣態的過程叫昇華；冰受熱則是先熔化成液態水，兩者狀態變化路徑不同，但都只是物理變化，沒有生成新物質</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>氧化</t>
+          <t>氧化：鐵在潮濕空氣中會和氧氣、水分反應，生成性質完全不同的氧化鐵(鐵鏽)這種新物質，所以是化學變化</t>
         </is>
       </c>
     </row>
